--- a/Result/profitability/8114.xlsx
+++ b/Result/profitability/8114.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3.845</v>
+        <v>3.94875</v>
       </c>
       <c r="N2" t="n">
-        <v>46.8925</v>
+        <v>46.00875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>3.59625</v>
+        <v>3.57</v>
       </c>
       <c r="N3" t="n">
-        <v>46.48999999999999</v>
+        <v>45.81</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.19125</v>
+        <v>2.90875</v>
       </c>
       <c r="N4" t="n">
-        <v>45.7075</v>
+        <v>44.42375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.46625</v>
+        <v>2.3</v>
       </c>
       <c r="N5" t="n">
-        <v>44.81375</v>
+        <v>43.28375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.82375</v>
+        <v>1.92</v>
       </c>
       <c r="N6" t="n">
-        <v>43.78125</v>
+        <v>43.145</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4875</v>
+        <v>1.6975</v>
       </c>
       <c r="N7" t="n">
-        <v>43.71625</v>
+        <v>43.16375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.96</v>
       </c>
       <c r="M8" t="n">
-        <v>1.275</v>
+        <v>1.47375</v>
       </c>
       <c r="N8" t="n">
-        <v>43.89375</v>
+        <v>42.95</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8114</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5183</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3138</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2045</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>964</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.59%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>975</v>
+      </c>
+      <c r="K75" t="n">
+        <v>467</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.20625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>45.95999999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5781818181818181</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.549999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1606382978723404</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2345679012345679</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-12.23999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2367962855484619</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
